--- a/销售数据.xlsx
+++ b/销售数据.xlsx
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,11 +68,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -84,6 +90,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1318,6 +1326,14 @@
           <t>华东</t>
         </is>
       </c>
+      <c r="B4">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A4,原始数据!$H$2:$H$21)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A4,原始数据!$G$2:$G$21)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1325,6 +1341,14 @@
           <t>华南</t>
         </is>
       </c>
+      <c r="B5">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A5,原始数据!$H$2:$H$21)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A5,原始数据!$G$2:$G$21)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1332,6 +1356,14 @@
           <t>华北</t>
         </is>
       </c>
+      <c r="B6">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A6,原始数据!$H$2:$H$21)</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A6,原始数据!$G$2:$G$21)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1339,6 +1371,14 @@
           <t>西南</t>
         </is>
       </c>
+      <c r="B7">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A7,原始数据!$H$2:$H$21)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A7,原始数据!$G$2:$G$21)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1346,6 +1386,14 @@
           <t>西北</t>
         </is>
       </c>
+      <c r="B8">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A8,原始数据!$H$2:$H$21)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>SUMIF(原始数据!$E$2:$E$21,$A8,原始数据!$G$2:$G$21)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1353,6 +1401,10 @@
           <t>总销售额</t>
         </is>
       </c>
+      <c r="B10">
+        <f>SUM(B4:B8)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1360,6 +1412,10 @@
           <t>平均订单金额</t>
         </is>
       </c>
+      <c r="B11">
+        <f>IF(SUM(C4:C8)=0,"",SUM(B4:B8)/SUM(C4:C8))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1367,45 +1423,62 @@
           <t>最大单笔金额</t>
         </is>
       </c>
+      <c r="B12">
+        <f>MAX(原始数据!H2:H21)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>订单查询</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>订单编号</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>SO-2607</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
+      <c r="B16" s="10">
+        <f>IFERROR(VLOOKUP($B$15,原始数据!$A$2:$H$21,3,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>产品</t>
         </is>
       </c>
+      <c r="B17" s="10">
+        <f>IFERROR(VLOOKUP($B$15,原始数据!$A$2:$H$21,4,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
+      </c>
+      <c r="B18" s="10">
+        <f>IFERROR(VLOOKUP($B$15,原始数据!$A$2:$H$21,8,0),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
